--- a/src/scrapers/output_scrape/vic/requirements_vic.xlsx
+++ b/src/scrapers/output_scrape/vic/requirements_vic.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,317 +433,323 @@
   </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>state code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>state stream</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>requirements</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>service fee</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="409" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Skilled_Nominated_Visa_Subclass_190</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Subclass_90</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>BASIC ELIGIBILITY
-  To be considered for Victorian skilled visa nomination, you must:
-- meet all the Australian Government's Department of Home Affair’s subclass 190 Skilled Nominated visa requirements.
-- meet all the Victorian Government’s subclass 190 Skilled Nominated visa nomination requirements.
+ To be considered for Victorian skilled visa nomination, you must:
+- meet all the Australian Government's Department of Home Affair's subclass 190 Skilled Nominated visa requirements.
+- meet all the Victorian Government's subclass 190 Skilled Nominated visa nomination requirements.
 VICTORIAN SUBCLASS 190 SKILLED VISA NOMINATION
-  [Who can apply?]
-  To be eligible to apply for Victorian Skilled Nominated (subclass 190) visa nomination, you must:
+ [Who can apply?]
+ To be eligible to apply for Victorian Skilled Nominated (subclass 190) visa nomination, you must:
 - be living in Victoria or overseas,
 - be committed to living and working in Victoria,
 - have had your Registration of Interest (ROI) selected,
 - be under 45 years of age,
 - have at least Competent English, external link
 - have a valid Skills Assessment external link in an occupation on the eligible skilled occupation list external link for this visa,
-- have achieved at least 65 points external link on the Australian Government’s points test for your Expression of Interest (EOI) in SkillSelect.
-  [How to apply?]
-  To apply for Victorian visa nomination, you must:
+- have achieved at least 65 points external link on the Australian Government's points test for your Expression of Interest (EOI) in SkillSelect.
+ [How to apply?]
+ To apply for Victorian visa nomination, you must:
 FURTHER ELIGIBILITY REQUIREMENTS
-  [Living in Victoria]
-  If you are living in Australia (onshore) you must be living in Victoria . We will not be selecting Registration of Interests (ROIs) from onshore applicants living in Australian states and territories other than Victoria. We do make some case-by-case exceptions for those living in border communities.
-  [Living overseas]
-  If you are living overseas (offshore), you are eligible to apply for Skilled Nominated (subclass 190) visa nomination. You must be committed to living in Victoria.
-  [Employment]
-  You are not required to be working to be eligible for Victorian subclass 190 visa nomination. There is no minimum work experience and hours of work requirement.
-  Living in Victoria (onshore):
+ [Living in Victoria]
+ If you are living in Australia (onshore) you must be living in Victoria . We will not be selecting Registration of Interests (ROIs) from onshore applicants living in Australian states and territories other than Victoria. We do make some case-by-case exceptions for those living in border communities.
+ [Living overseas]
+ If you are living overseas (offshore), you are eligible to apply for Skilled Nominated (subclass 190) visa nomination. You must be committed to living in Victoria.
+ [Employment]
+ You are not required to be working to be eligible for Victorian subclass 190 visa nomination. There is no minimum work experience and hours of work requirement.
+ Living in Victoria (onshore):
 - If you are living in Victoria and work in skilled employment for an employer physically located in Victoria , you can provide an estimate of your annual earnings in your ROI . A business using a virtual office or proxy office is not considered as physically located in Victoria. Your employment does not have to be related to or the same as your nominated occupation, but your earnings must be from skilled employment in Victoria. View our Annual earnings estimation guide for information on skilled employment and what you can and cannot claim.
 - If you are not working, working in non-skilled employment, or working for an employer not physically located in Victoria, you are still eligible to apply for nomination, but you are not eligible to claim earnings in your ROI.
-  Living overseas (offshore):
+ Living overseas (offshore):
 - If you are living overseas, you are not required to claim earnings in your ROI.
-  [Commitment to Victoria]
+ [Commitment to Victoria]
 - You must be committed to living and working in Victoria.
 - State nomination cannot be transferred from one state to another.
-  [Registration of Interest]
+ [Registration of Interest]
 - To be invited to apply for Victorian visa nomination, you must submit an ROI.
 - Your ROI must be selected by us before you can apply for skilled visa nomination. An ROI is not an application for Victorian visa nomination. There is no guarantee that your ROI will be selected.
 - View our Registration of Interest page for more information on assessment and selection considerations.
-  [Age]
+ [Age]
 - You must be under 45 years of age at the time of nomination. This is a Department of Home Affairs requirement.
-  [English language]
+ [English language]
 - You must have at least Competent English external link .
 - When you submit your nomination application, we require that your English test has at least 12 weeks validity remaining. This ensures we have enough time to assess your nomination application. We cannot nominate you if your English test has expired.
-- For further information, see the Australian Government's Department of Home Affairs’ English language requirements external link page.
-  [Skills Assessment]
-- You must have a valid skills assessment in an occupation on the Australian Government’s eligible skilled occupation list external link for the visa.
+- For further information, see the Australian Government's Department of Home Affairs' English language requirements external link page.
+ [Skills Assessment]
+- You must have a valid skills assessment in an occupation on the Australian Government's eligible skilled occupation list external link for the visa.
 - Your nominated occupation in your Skills Assessment external link must match your SkillSelect Expression of Interest (EOI) with the Department of Home Affairs.
 - When you submit your nomination application, we require that your Skills Assessment external link has at least 12 weeks validity remaining. This ensures we have enough time to assess your nomination application. We cannot nominate you if your Skills Assessment has expired.
-- For Health professionals, your occupation must be consistent with your Australian Health Practitioner Regulation Agency (AHPRA) registration.
-  [SkillSelect EOI Points]
-- You must have at least 65 points on the Australian Government’s points test external link , including the 5 points for state and territory nomination.
+- For Health professionals, your occupation must be consistent with your Australian Health Practitioner Regulation Agency (AHPRA) registration.
+ [SkillSelect EOI Points]
+- You must have at least 65 points on the Australian Government's points test external link , including the 5 points for state and territory nomination.
 INVITATION TO APPLY FOR VICTORIAN NOMINATION
-  To be invited to apply for Victorian skilled visa nomination, you must firstly make or update an Expression of Interest via the Australian Government’s SkillSelect external link and then submit a Registration of Interest (ROI).
-  View our Registration of Interest page for more information on ROI assessment and selection considerations.
-  For information on how to calculate your estimated annual earnings, visit our Annual Earnings Estimation Guide page. Answers to frequently asked questions can be found on our Skilled Visa FAQs page.
+ To be invited to apply for Victorian skilled visa nomination, you must firstly make or update an Expression of Interest via the Australian Government's SkillSelect external link and then submit a Registration of Interest (ROI).
+ View our Registration of Interest page for more information on ROI assessment and selection considerations.
+ For information on how to calculate your estimated annual earnings, visit our Annual Earnings Estimation Guide page. Answers to frequently asked questions can be found on our Skilled Visa FAQs page.
 SUBMITTING A NOMINATION APPLICATION
-  [Submit your application via the portal]
-  If you are invited to apply, you or your agent (if applicable) will be notified via email.
-  You must submit your application and all documents via the Live in Melbourne portal external link . We will not accept any applications or documents via email.
-  [What documents you will need]
-  If you are invited to apply for Victorian nomination, you must submit a complete application, including all relevant evidence to support your eligibility claims.
-  In your Victorian nomination application, you may need to provide the following documents to show you meet the requirements:
+ [Submit your application via the portal]
+ If you are invited to apply, you or your agent (if applicable) will be notified via email.
+ You must submit your application and all documents via the Live in Melbourne portal external link . We will not accept any applications or documents via email.
+ [What documents you will need]
+ If you are invited to apply for Victorian nomination, you must submit a complete application, including all relevant evidence to support your eligibility claims.
+ In your Victorian nomination application, you may need to provide the following documents to show you meet the requirements:
 - passport,
 - evidence of Victorian residence.
-  During the assessment of your nomination application, we may ask for further evidence and additional documents.
-  [Living in Victoria:]
-  To prove your residence in Victoria, you may be asked to provide the following documents to show you meet the requirements:
+ During the assessment of your nomination application, we may ask for further evidence and additional documents.
+ [Living in Victoria:]
+ To prove your residence in Victoria, you may be asked to provide the following documents to show you meet the requirements:
 - bank statements for a minimum of 6 months from your main transaction account showing your salary and everyday transactions,
 - rental or lease agreements,
 - utility bills e.g. gas, water, phone, internet,
-- driver’s licence or proof of age cards.
-  If you included annual earnings in your Registration of Interest (ROI) you will also need to provide the following in your nomination application:
+- driver's licence or proof of age cards.
+ If you included annual earnings in your Registration of Interest (ROI) you will also need to provide the following in your nomination application:
 - employment contract,
 - position description detailing the duration of your employment, the hours worked per week, and duties performed,
 - payslips (at least most recent four weeks),
 - superannuation statement (showing most recent contributions), or
 - your letter of offer.
 NOMINATION APPLICATION ASSESSMENT
-  If you submit a nomination application, it will be assessed by the Victorian Government. You will be notified of the outcome by email as soon as a decision has been made.
-  [Respond within two weeks]
-  We may ask you for more information by email.
+ If you submit a nomination application, it will be assessed by the Victorian Government. You will be notified of the outcome by email as soon as a decision has been made.
+ [Respond within two weeks]
+ We may ask you for more information by email.
 - You will have two weeks to provide the requested information.
 - If you do not respond within two weeks, we may refuse your application. Please check your junk mail and ensure the email address no-reply-gems@liveinmelbourne.vic.gov.au external link is added to your list of valid email addresses.
-  [Incomplete applications]
-  You must submit a complete application, including all relevant evidence to support your eligibility claims.
-  [Do not ask for updates on your application]
-  Please do not ask for an update on your application. We assess all applications in order of when they are submitted.
-  If you have submitted a nomination application with us, you or your agent (if applicable) can check the status of your application through the Live in Melbourne portal. The average processing time for skilled visa nomination applications is 20 business days. This does not include the waiting time if we require additional information for your application.
-  The assessment team is also responsible for responding to enquiries and we prioritise assessment of applications. Unnecessary enquiries slow down application processing times.
-  [Withdrawal]
-  You can only withdraw your subclass 190 nomination application before we finalise our assessment. Please Contact Us to withdraw your nomination application.
-  For Registrations of Interest (ROIs), you must withdraw your ROI using the Live in Melbourne portal. external link
+ [Incomplete applications]
+ You must submit a complete application, including all relevant evidence to support your eligibility claims.
+ [Do not ask for updates on your application]
+ Please do not ask for an update on your application. We assess all applications in order of when they are submitted.
+ If you have submitted a nomination application with us, you or your agent (if applicable) can check the status of your application through the Live in Melbourne portal. The average processing time for skilled visa nomination applications is 20 business days. This does not include the waiting time if we require additional information for your application.
+ The assessment team is also responsible for responding to enquiries and we prioritise assessment of applications. Unnecessary enquiries slow down application processing times.
+ [Withdrawal]
+ You can only withdraw your subclass 190 nomination application before we finalise our assessment. Please Contact Us to withdraw your nomination application.
+ For Registrations of Interest (ROIs), you must withdraw your ROI using the Live in Melbourne portal. external link
 NOMINATION APPLICATION OUTCOME
-  [Once you are nominated]
-  [Nomination refusals]
-  Before submitting a Registration of Interest (ROI) make sure you meet all the minimum eligibility requirements for the visa you are seeking nomination for.
-  Your nomination application will be refused for the following reasons:
+ [Once you are nominated]
+ [Nomination refusals]
+ Before submitting a Registration of Interest (ROI) make sure you meet all the minimum eligibility requirements for the visa you are seeking nomination for.
+ Your nomination application will be refused for the following reasons:
 - You do not meet the minimum eligibility requirements.
 - You cannot provide sufficient evidence for the claims made in your ROI or SkillSelect EOI.
 - You do not respond to our requests for further information in a timely manner.
 - You provide false or misleading information.
-  Common reasons for refused applications include:
+ Common reasons for refused applications include:
 - Over-estimated earnings (for onshore).
 - Working in employment that is not eligible (for onshore).
 - Working for an employer not operating in Victoria (for onshore).
 - Living in an Australian state and territory other than Victoria (for onshore)
 - Incorrect partner points.
-- Modification of SkillSelect EOI after invitation.
+- Modification of SkillSelect EOI after invitation.
 - False and misleading information related to employment and residence.
 - Expired Skills Assessment or English language test results.
-  If you are unable to provide sufficient evidence to demonstrate the claims you make in your SkillSelect EOI and ROI, your application may be refused.
-  If your application is refused, you will not be able to submit a new application for 6 months. This ensures our resources are allocated to processing applications that meet the requirements of the visa.
-  [False and misleading information]
-  If you provide false or misleading information as part of your nomination application, your application will be refused. We may also report it to the Department of Home Affairs who can conduct their own investigation.
-  We encourage you to submit all documents unaltered, including all PDF documents in their original form and not combined into one document.
-  We conduct verification checks on many of the documents you provide to ensure that your employment matches the skill level of your nominated occupation that you outline in your SkillSelect EOI. This includes contacting employers and institutions directly to confirm whether the documents are genuine.
-  If you are aware of instances, or yourself are pressured to submit an application with false and misleading information, we encourage you to report this to the Department of Home Affairs.
-  [Review of nomination decision]
-  If your nomination application has been refused as you did not meet the eligibility requirements, you cannot request a review of your application.
-  If you believe that an error was made in assessing your nomination application, you can submit a request for us to review the application.
-  [Renomination]
-  We do not provide renomination in the following instances:
+ If you are unable to provide sufficient evidence to demonstrate the claims you make in your SkillSelect EOI and ROI, your application may be refused.
+ If your application is refused, you will not be able to submit a new application for 6 months. This ensures our resources are allocated to processing applications that meet the requirements of the visa.
+ [False and misleading information]
+ If you provide false or misleading information as part of your nomination application, your application will be refused. We may also report it to the Department of Home Affairs who can conduct their own investigation.
+ We encourage you to submit all documents unaltered, including all PDF documents in their original form and not combined into one document.
+ We conduct verification checks on many of the documents you provide to ensure that your employment matches the skill level of your nominated occupation that you outline in your SkillSelect EOI. This includes contacting employers and institutions directly to confirm whether the documents are genuine.
+ If you are aware of instances, or yourself are pressured to submit an application with false and misleading information, we encourage you to report this to the Department of Home Affairs.
+ [Review of nomination decision]
+ If your nomination application has been refused as you did not meet the eligibility requirements, you cannot request a review of your application.
+ If you believe that an error was made in assessing your nomination application, you can submit a request for us to review the application.
+ [Renomination]
+ We do not provide renomination in the following instances:
 - You do not submit your visa application within 60 days.
 - Your SkillSelect EOI was incorrect when we nominated you, including points claimed by you or your agent.
-  If an applicant has been nominated for any skilled subclass (either 190 or 491), they cannot be nominated again in the same program year.
+ If an applicant has been nominated for any skilled subclass (either 190 or 491), they cannot be nominated again in the same program year.
 YOUR NOMINATION OBLIGATIONS
-  [Declaration form]
-  If you are nominated, you must meet the nomination obligations that you signed in the declaration form .
-  [Surveys]
-  If you are nominated, we will contact you at various times.
-  In the declaration form, you agree to complete surveys if requested by, or on behalf of the Victorian Government, including a survey upon arrival and at six monthly intervals for the two years after visa grant or arrival in Australia.
-  These surveys are a condition of nomination. They provide us important feedback on our client services and policy settings. The surveys do not have an impact on your visa.
-  [Department of Home Affairs and SkillSelect]
-  The Australian Government's Department of Home Affairs external link is responsible for all visa matters. This includes once you have been nominated by the Victorian Government and have submitted your visa application.
-  Please check subclass 190 visa processing times external link published by the Department of Home Affairs.
-  All SkillSelect and Expressions of Interest (EOI) enquiries should be directed to the Department of Home Affairs.
+ [Declaration form]
+ If you are nominated, you must meet the nomination obligations that you signed in the declaration form .
+ [Surveys]
+ If you are nominated, we will contact you at various times.
+ In the declaration form, you agree to complete surveys if requested by, or on behalf of the Victorian Government, including a survey upon arrival and at six monthly intervals for the two years after visa grant or arrival in Australia.
+ These surveys are a condition of nomination. They provide us important feedback on our client services and policy settings. The surveys do not have an impact on your visa.
+ [Department of Home Affairs and SkillSelect]
+ The Australian Government's Department of Home Affairs external link is responsible for all visa matters. This includes once you have been nominated by the Victorian Government and have submitted your visa application.
+ Please check subclass 190 visa processing times external link published by the Department of Home Affairs.
+ All SkillSelect and Expressions of Interest (EOI) enquiries should be directed to the Department of Home Affairs.
 TERMS AND CONDITIONS
-  [Can my employer or family member represent me as an agent for Victorian nomination?]
-  No, you cannot appoint an agent to act on your behalf if there are personal, financial or other interests that could, or could be seen to, influence their representation of you.
-  If a conflict of interest is identified during the application assessment, the Appointment of Agent will be deemed invalid, and the application may be refused.
-  [Nomination application fees]
-  Victorian Registration of Interest (ROI) and nomination are free of charge. When you submit your visa application with the Australian Government's Department of Home Affairs, you will need to pay the visa fee.
-  [Changes to eligibility requirements]
-  All visa nomination eligibility requirements and priorities are subject to change throughout the year without notice.
-  Any changes made are effective immediately, regardless of when your SkillSelect Expression of Interest (EOI) was submitted (or amended). We strongly discourage changing your circumstances to meet the visa nomination criteria.
-  The Victorian Government endeavours to ensure all information on the Live in Melbourne website reflects the current eligibility requirements. The Live in Melbourne website is the authoritative source for information about Victoria's skilled visa nomination program.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+ [Can my employer or family member represent me as an agent for Victorian nomination?]
+ No, you cannot appoint an agent to act on your behalf if there are personal, financial or other interests that could, or could be seen to, influence their representation of you.
+ If a conflict of interest is identified during the application assessment, the Appointment of Agent will be deemed invalid, and the application may be refused.
+ [Nomination application fees]
+ Victorian Registration of Interest (ROI) and nomination are free of charge. When you submit your visa application with the Australian Government's Department of Home Affairs, you will need to pay the visa fee.
+ [Changes to eligibility requirements]
+ All visa nomination eligibility requirements and priorities are subject to change throughout the year without notice.
+ Any changes made are effective immediately, regardless of when your SkillSelect Expression of Interest (EOI) was submitted (or amended). We strongly discourage changing your circumstances to meet the visa nomination criteria.
+ The Victorian Government endeavours to ensure all information on the Live in Melbourne website reflects the current eligibility requirements. The Live in Melbourne website is the authoritative source for information about Victoria's skilled visa nomination program.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="409" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Skilled_Work_Regional_Visa_Subclass_491</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Subclass_491</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>BASIC ELIGIBILITY
-  To be considered for Victorian skilled visa nomination, you must:
+ To be considered for Victorian skilled visa nomination, you must:
 - Meet all the Department of Home Affairs - subclass 491 Skilled Work Regional (Provisional) visa requirements external link .
-- Meet all the Victorian Government’s - subclass 491Skilled Nominated visa requirements.
+- Meet all the Victorian Government's - subclass 491Skilled Nominated visa requirements.
 VICTORIAN SUBCLASS 491 SKILLED WORK REGIONAL VISA NOMINATION
-  [Who can apply?]
-  To be eligible to apply for Skilled Work Regional (Provisional) visa (subclass 491) nomination, you must:
+ [Who can apply?]
+ To be eligible to apply for Skilled Work Regional (Provisional) visa (subclass 491) nomination, you must:
 - be one of the following: living offshore living and working in regional Victoria.
 - be committed to living and working in regional Victoria,
 - have had your Registration of Interest (ROI) selected,
 - be under 45 years of age,
 - have at least Competent English external link ,
 - have a valid skills assessment external link in an occupation on the eligible skilled occupation list external link for this visa,
-- have achieved at least 65 points external link on the Australian Government’s points test for your Expression of Interest (EOI) in SkillSelect external link .
+- have achieved at least 65 points external link on the Australian Government's points test for your Expression of Interest (EOI) in SkillSelect external link .
 - living offshore
 - living and working in regional Victoria.
-  [How to apply?]
-  To apply for Victorian visa nomination, you must:
+ [How to apply?]
+ To apply for Victorian visa nomination, you must:
 FURTHER ELIGIBILITY REQUIREMENTS
-  [Living overseas]
-  Residence
-  If you are living overseas (offshore), you are eligible to apply for Skilled Work Regional (Provisional) visa (subclass 491) visa nomination.
-  Once you are granted the subclass 491 visa you will be required to relocate to regional Victoria. The conditions of the subclass 491 visa require you, and any dependent applicants, to live, work, and study in a designated regional area.
-  Employment
-  If you are living overseas, you are not required to claim earnings in your ROI .
-  [Living in Victoria]
-  Residence
-  You must be living in regional Victoria external link .
-- Some outer suburbs of Melbourne are considered regional for the purposes of migration by the Australian's Government's Department of Home Affairs. For example, the Mornington Peninsula, Pakenham and Geelong are considered designated regional areas of Victoria for migration purposes.
+ [Living overseas]
+ Residence
+ If you are living overseas (offshore), you are eligible to apply for Skilled Work Regional (Provisional) visa (subclass 491) visa nomination.
+ Once you are granted the subclass 491 visa you will be required to relocate to regional Victoria. The conditions of the subclass 491 visa require you, and any dependent applicants, to live, work, and study in a designated regional area.
+ Employment
+ If you are living overseas, you are not required to claim earnings in your ROI .
+ [Living in Victoria]
+ Residence
+ You must be living in regional Victoria external link .
+- Some outer suburbs of Melbourne are considered regional for the purposes of migration by the Australian's Government's Department of Home Affairs. For example, the Mornington Peninsula, Pakenham and Geelong are considered designated regional areas of Victoria for migration purposes.
 - You can find information about the designated regional areas external link on the Department of Home Affairs website.
 - We make case-by-case exceptions for those living in border communities.
-  The conditions of the subclass 491 visa require you, and any dependent applicants, to live, work, and study in a designated regional area.
-  Employment
-- You must be working in skilled employment for an employer physically located in regional Victoria. A business using a virtual office or proxy office is not considered as physically located in regional Victoria.
+ The conditions of the subclass 491 visa require you, and any dependent applicants, to live, work, and study in a designated regional area.
+ Employment
+- You must be working in skilled employment for an employer physically located in regional Victoria. A business using a virtual office or proxy office is not considered as physically located in regional Victoria.
 - A business using a virtual office or proxy office is not considered as physically located in regional Victoria.
-- You must provide an estimate of your annual earnings in your ROI . Your earnings must be from skilled employment in regional Victoria. View our Annual earnings estimation guide for information on skilled employment and what you can and cannot claim.
+- You must provide an estimate of your annual earnings in your ROI . Your earnings must be from skilled employment in regional Victoria. View our Annual earnings estimation guide for information on skilled employment and what you can and cannot claim.
 - View our Annual earnings estimation guide for information on skilled employment and what you can and cannot claim.
 - Your employment does not have to be related to or the same as your nominated occupation.
 - There is no minimum requirement for hours worked.
 - If you are not working, working in non-skilled employment, or working for an employer who is not physically located in regional Victoria, you are not eligible to apply for nomination.
-  [Commitment to regional Victoria]
+ [Commitment to regional Victoria]
 - You must be committed to living and working in a designated regional area of Victoria external link .
 - State nomination cannot be transferred from one state to another.
-  [Registration of Interest]
+ [Registration of Interest]
 - To be invited to apply for Victorian visa nomination, you must submit an ROI.
 - Your ROI must be selected by us before you can apply for skilled visa nomination. An ROI is not an application for Victorian visa nomination. There is no guarantee that your ROI will be selected.
 - View our Registration of Interest page for more information on assessment and selection considerations.
-  [Age]
+ [Age]
 - You must be under 45 years of age at the time of nomination. This is a Department of Home Affairs requirement.
-  [English language]
+ [English language]
 - You must have at least Competent English external link .
 - When you submit your nomination application, we require that your English language test has at least 12 weeks validity remaining. This ensures we have enough time to assess your nomination application. We cannot nominate you if your English language test has expired.
 - For further information, see the Australian Government's Department of Home Affairs English language requirements external link page.
-  [Skills Assessment]
+ [Skills Assessment]
 - You must have a valid skills assessment in an occupation on the eligible skilled occupation list external link for the visa.
 - Your nominated occupation in your Skills Assessment external link must match your Expression of Interest with the Department of Home Affairs.
 - When you submit your nomination application, we require that your Skills Assessment has at least 12 weeks validity remaining. This ensures we have enough time to assess your nomination application. We cannot nominate you if your Skills Assessment has expired.
-- For Health professionals, your occupation must be consistent with your Australian Health Practitioner Regulation Agency (AHPRA) registration.
-  [SkillSelect EOI Points]
-- You must have at least 65 points external link on the Australian Government’s points test external link , including the 15 points for state and territory nomination.
+- For Health professionals, your occupation must be consistent with your Australian Health Practitioner Regulation Agency (AHPRA) registration.
+ [SkillSelect EOI Points]
+- You must have at least 65 points external link on the Australian Government's points test external link , including the 15 points for state and territory nomination.
 INVITATION TO APPLY FOR VICTORIAN NOMINATION
-  To be invited to apply for Victorian skilled visa nomination, you must firstly submit or update an Expression of Interest via the Australian Government’s SkillSelect and then submit a Registration of Interest (ROI).
-  View our Registration of Interest page for more information on ROI assessment and selection considerations.
-  For information on how to calculate your estimated annual earnings, visit our Annual Earnings Estimation Guide page. Answers to frequently asked questions can be found on our Skilled Visa FAQs page.
+ To be invited to apply for Victorian skilled visa nomination, you must firstly submit or update an Expression of Interest via the Australian Government's SkillSelect and then submit a Registration of Interest (ROI).
+ View our Registration of Interest page for more information on ROI assessment and selection considerations.
+ For information on how to calculate your estimated annual earnings, visit our Annual Earnings Estimation Guide page. Answers to frequently asked questions can be found on our Skilled Visa FAQs page.
 SUBMITTING A NOMINATION APPLICATION
-  [Submit your application via the portal]
-  If you are invited to apply, you or your agent (if applicable) will be notified via email.
-  You must submit your application and all documents via the Live in Melbourne portal external link . We will not accept any applications or documents via email.
-  [What documents you will need]
-  If you are invited to apply for Victorian nomination, you must submit a complete application, including all relevant evidence to support your eligibility claims.
-  In your Victorian nomination application, you may need to provide the following documents to show you meet the requirements:
+ [Submit your application via the portal]
+ If you are invited to apply, you or your agent (if applicable) will be notified via email.
+ You must submit your application and all documents via the Live in Melbourne portal external link . We will not accept any applications or documents via email.
+ [What documents you will need]
+ If you are invited to apply for Victorian nomination, you must submit a complete application, including all relevant evidence to support your eligibility claims.
+ In your Victorian nomination application, you may need to provide the following documents to show you meet the requirements:
 - passport,
 - evidence of Victorian residence.
-  During the assessment of your nomination application, we may ask for further evidence and additional documents.
-  Living in regional Victoria:
-  To prove your residence in regional Victoria, you may be asked to provide the following documents to show you meet the requirements:
+ During the assessment of your nomination application, we may ask for further evidence and additional documents.
+ Living in regional Victoria:
+ To prove your residence in regional Victoria, you may be asked to provide the following documents to show you meet the requirements:
 - bank statements for a minimum of 6 months from your main transaction account showing your salary and everyday transactions,
 - rental or lease agreements,
 - utility bills e.g. gas, water, phone, internet,
-- driver’s licence or proof of age cards.
-  If you included annual earnings in your Registration of Interest (ROI) you will also need to provide the following in your nomination application:
+- driver's licence or proof of age cards.
+ If you included annual earnings in your Registration of Interest (ROI) you will also need to provide the following in your nomination application:
 - employment contract,
 - position description detailing the duration of your employment, the hours worked per week and duties performed
 - payslips (at least most recent four weeks),
 - superannuation statement (showing most recent contributions),
 - your letter of offer.
 NOMINATION APPLICATION ASSESSMENT
-  Following submission of your nomination application, you will be notified of the outcome by email as soon as a decision has been made.
-  [Respond within two weeks]
-  We may ask you for more information by email.
+ Following submission of your nomination application, you will be notified of the outcome by email as soon as a decision has been made.
+ [Respond within two weeks]
+ We may ask you for more information by email.
 - You will have two weeks to provide the requested information.
 - If you do not respond within two weeks, we may refuse your application. Please check your junk mail and ensure the email address no-reply-gems@liveinmelbourne.vic.gov.au external link is added to your list of valid email addresses.‎‎‎
-  [Incomplete applications]
-  You must submit a complete application, including all relevant evidence to support your eligibility claims.
-  [Please do not ask for updates on your application]
-  Please do not ask for an update on your application. We assess all applications in order of when they are submitted.
-  If you have submitted a nomination application, you or your agent (if applicable) can check the status of your application through the Live in Melbourne portal. external link The average processing time for skilled visa nomination applications is 20 business days. This does not include the waiting time if we require additional information for your application.
-  The assessment team is also responsible for responding to enquiries and we prioritise assessment of applications. Unnecessary enquiries slow down application processing times.
-  [Withdrawal]
-  You can only withdraw your subclass 491 nomination application before we finalise our assessment. Please Contact Us to withdraw your nomination application.
-  For Registrations of Interest (ROI), you must withdraw your ROI using the Live in Melbourne portal external link .
+ [Incomplete applications]
+ You must submit a complete application, including all relevant evidence to support your eligibility claims.
+ [Please do not ask for updates on your application]
+ Please do not ask for an update on your application. We assess all applications in order of when they are submitted.
+ If you have submitted a nomination application, you or your agent (if applicable) can check the status of your application through the Live in Melbourne portal. external link The average processing time for skilled visa nomination applications is 20 business days. This does not include the waiting time if we require additional information for your application.
+ The assessment team is also responsible for responding to enquiries and we prioritise assessment of applications. Unnecessary enquiries slow down application processing times.
+ [Withdrawal]
+ You can only withdraw your subclass 491 nomination application before we finalise our assessment. Please Contact Us to withdraw your nomination application.
+ For Registrations of Interest (ROI), you must withdraw your ROI using the Live in Melbourne portal external link .
 NOMINATION APPLICATION OUTCOME
-  [Once you are nominated]
-  [Nomination refusals]
-  Before submitting a Registration of Interest (ROI) make sure you meet all the minimum eligibility requirements for the visa you are seeking nomination for.
-  Your nomination application will be refused for the following reasons:
+ [Once you are nominated]
+ [Nomination refusals]
+ Before submitting a Registration of Interest (ROI) make sure you meet all the minimum eligibility requirements for the visa you are seeking nomination for.
+ Your nomination application will be refused for the following reasons:
 - You do not meet the minimum eligibility requirements.
 - You cannot provide sufficient evidence for the claims made in your ROI or SkillSelect EOI.
 - You provide false or misleading information.
 - You do not respond to our requests for further information in a timely manner.
-  Common reasons for refused applications include:
+ Common reasons for refused applications include:
 - Over-estimated earnings (for onshore).
 - Working in a non-skilled employment (for onshore).
 - Working for an employer not operating in regional Victoria (for onshore).
@@ -734,45 +758,45 @@
 - Modification of your SkillSelect EOI after invitation.
 - Integrity concerns with residence and employment claims.
 - Skills assessment or English language test result expired.
-  If you are unable to provide sufficient evidence to demonstrate the claims you make in your SkillSelect EOI and ROI, your application may be refused.
-  If your application is refused, you will not be able to submit a new application for 6 months. This ensures our resources are allocated to processing applications that meet the requirements of the visa.
-  [False and misleading information]
-  If you provide false or misleading information as part of your nomination application, your application will be refused. We may also report it to the Department of Home Affairs who can conduct their own investigation.
-  We encourage you to submit all documents unaltered, including all PDF documents in their original form and not combined into one document.
-  We conduct verification checks on many of the documents you provide to ensure that your employment matches the skill level of your nominated occupation that you outline in your SkillSelect EOI. This includes contacting employers and institutions directly to confirm whether the documents are genuine.
-  If you are aware of instances, or yourself are pressured to submit an application with false and misleading information, we encourage you to report this to the Department of Home Affairs.
-  [Review of nomination decision]
-  If your nomination application has been refused as you did not meet the eligibility requirements, you cannot request a review of your application.
-  If you believe that an error was made in assessing your nomination application, you can submit a request for us to review the application.
-  [Renomination]
-  We do not provide renomination in the following instances:
+ If you are unable to provide sufficient evidence to demonstrate the claims you make in your SkillSelect EOI and ROI, your application may be refused.
+ If your application is refused, you will not be able to submit a new application for 6 months. This ensures our resources are allocated to processing applications that meet the requirements of the visa.
+ [False and misleading information]
+ If you provide false or misleading information as part of your nomination application, your application will be refused. We may also report it to the Department of Home Affairs who can conduct their own investigation.
+ We encourage you to submit all documents unaltered, including all PDF documents in their original form and not combined into one document.
+ We conduct verification checks on many of the documents you provide to ensure that your employment matches the skill level of your nominated occupation that you outline in your SkillSelect EOI. This includes contacting employers and institutions directly to confirm whether the documents are genuine.
+ If you are aware of instances, or yourself are pressured to submit an application with false and misleading information, we encourage you to report this to the Department of Home Affairs.
+ [Review of nomination decision]
+ If your nomination application has been refused as you did not meet the eligibility requirements, you cannot request a review of your application.
+ If you believe that an error was made in assessing your nomination application, you can submit a request for us to review the application.
+ [Renomination]
+ We do not provide renomination in the following instances:
 - You do not submit your visa application within 60 days.
 - Your SkillSelect EOI was incorrect when we nominated you, including points claimed by you or your agent.
-  If an applicant has been nominated for any skilled visa (either subclass 190 or 491), they cannot be nominated again in the same program year.
+ If an applicant has been nominated for any skilled visa (either subclass 190 or 491), they cannot be nominated again in the same program year.
 YOUR NOMINATION OBLIGATIONS
-  [Declaration form]
-  If you are nominated, you must meet the nomination obligations that you signed in the declaration form .
-  [Surveys]
-  If you are nominated, we will contact you at various times.
-  In the declaration form, you agree to complete surveys if requested by, or on behalf of the Victorian Government, including a survey upon arrival and at six monthly intervals for the three years after visa grant or arrival in Australia.
-  These surveys are a condition of nomination. They provide us important feedback on our client services and policy settings.
-  [Department of Home Affairs and SkillSelect]
-  The Australian Government's Department of Home Affairs external link is responsible for all visa matters. This includes once you have been nominated by the Victorian Government and have submitted your visa application.
-  Please check subclass 491 visa processing times external link published by the Department of Home Affairs.
-  All SkillSelect and Expression of Interest enquiries should be directed to the Department of Home Affairs .
+ [Declaration form]
+ If you are nominated, you must meet the nomination obligations that you signed in the declaration form .
+ [Surveys]
+ If you are nominated, we will contact you at various times.
+ In the declaration form, you agree to complete surveys if requested by, or on behalf of the Victorian Government, including a survey upon arrival and at six monthly intervals for the three years after visa grant or arrival in Australia.
+ These surveys are a condition of nomination. They provide us important feedback on our client services and policy settings.
+ [Department of Home Affairs and SkillSelect]
+ The Australian Government's Department of Home Affairs external link is responsible for all visa matters. This includes once you have been nominated by the Victorian Government and have submitted your visa application.
+ Please check subclass 491 visa processing times external link published by the Department of Home Affairs.
+ All SkillSelect and Expression of Interest enquiries should be directed to the Department of Home Affairs .
 TERMS AND CONDITIONS
-  [Can my employer or family member represent me as an agent for Victorian nomination?]
-  No, you cannot appoint an agent to act on your behalf if there are personal, financial or other interests that could, or could be seen to, influence their representation of you.
-  If a conflict of interest is identified during the application assessment, the Appointment of Agent will be deemed invalid, and the application may be refused.
-  [Nomination application fees]
-  Victorian Registration of Interest (ROI) and nomination are free of charge. When you submit your visa application with the Australian Government's Department of Home Affairs, you will need to pay the visa fee.
-  [Changes to eligibility requirements]
-  All visa nomination eligibility requirements and priorities are subject to change throughout the year without notice.
-  Any changes made are effective immediately, regardless of when your SkillSelect Expression of Interest (EOI) was submitted (or amended). We strongly discourage changing your circumstances to meet the visa nomination criteria.
-  The Victorian Government endeavours to ensure all information on the Live in Melbourne website reflects the current eligibility requirements. The Live in Melbourne website is the authoritative source for information about Victoria's skilled visa nomination program.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+ [Can my employer or family member represent me as an agent for Victorian nomination?]
+ No, you cannot appoint an agent to act on your behalf if there are personal, financial or other interests that could, or could be seen to, influence their representation of you.
+ If a conflict of interest is identified during the application assessment, the Appointment of Agent will be deemed invalid, and the application may be refused.
+ [Nomination application fees]
+ Victorian Registration of Interest (ROI) and nomination are free of charge. When you submit your visa application with the Australian Government's Department of Home Affairs, you will need to pay the visa fee.
+ [Changes to eligibility requirements]
+ All visa nomination eligibility requirements and priorities are subject to change throughout the year without notice.
+ Any changes made are effective immediately, regardless of when your SkillSelect Expression of Interest (EOI) was submitted (or amended). We strongly discourage changing your circumstances to meet the visa nomination criteria.
+ The Victorian Government endeavours to ensure all information on the Live in Melbourne website reflects the current eligibility requirements. The Live in Melbourne website is the authoritative source for information about Victoria's skilled visa nomination program.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/src/scrapers/output_scrape/vic/requirements_vic.xlsx
+++ b/src/scrapers/output_scrape/vic/requirements_vic.xlsx
@@ -46,8 +46,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,317 +418,323 @@
   </sheetPr>
   <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>state code</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>state stream</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>requirements</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>service fee</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="409" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Skilled_Nominated_Visa_Subclass_190</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>Subclass_190</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>BASIC ELIGIBILITY
-  To be considered for Victorian skilled visa nomination, you must:
-- meet all the Australian Government's Department of Home Affair’s subclass 190 Skilled Nominated visa requirements.
-- meet all the Victorian Government’s subclass 190 Skilled Nominated visa nomination requirements.
+ To be considered for Victorian skilled visa nomination, you must:
+- meet all the Australian Government's Department of Home Affair's subclass 190 Skilled Nominated visa requirements.
+- meet all the Victorian Government's subclass 190 Skilled Nominated visa nomination requirements.
 VICTORIAN SUBCLASS 190 SKILLED VISA NOMINATION
-  [Who can apply?]
-  To be eligible to apply for Victorian Skilled Nominated (subclass 190) visa nomination, you must:
+ [Who can apply?]
+ To be eligible to apply for Victorian Skilled Nominated (subclass 190) visa nomination, you must:
 - be living in Victoria or overseas,
 - be committed to living and working in Victoria,
 - have had your Registration of Interest (ROI) selected,
 - be under 45 years of age,
 - have at least Competent English, external link
 - have a valid Skills Assessment external link in an occupation on the eligible skilled occupation list external link for this visa,
-- have achieved at least 65 points external link on the Australian Government’s points test for your Expression of Interest (EOI) in SkillSelect.
-  [How to apply?]
-  To apply for Victorian visa nomination, you must:
+- have achieved at least 65 points external link on the Australian Government's points test for your Expression of Interest (EOI) in SkillSelect.
+ [How to apply?]
+ To apply for Victorian visa nomination, you must:
 FURTHER ELIGIBILITY REQUIREMENTS
-  [Living in Victoria]
-  If you are living in Australia (onshore) you must be living in Victoria . We will not be selecting Registration of Interests (ROIs) from onshore applicants living in Australian states and territories other than Victoria. We do make some case-by-case exceptions for those living in border communities.
-  [Living overseas]
-  If you are living overseas (offshore), you are eligible to apply for Skilled Nominated (subclass 190) visa nomination. You must be committed to living in Victoria.
-  [Employment]
-  You are not required to be working to be eligible for Victorian subclass 190 visa nomination. There is no minimum work experience and hours of work requirement.
-  Living in Victoria (onshore):
+ [Living in Victoria]
+ If you are living in Australia (onshore) you must be living in Victoria . We will not be selecting Registration of Interests (ROIs) from onshore applicants living in Australian states and territories other than Victoria. We do make some case-by-case exceptions for those living in border communities.
+ [Living overseas]
+ If you are living overseas (offshore), you are eligible to apply for Skilled Nominated (subclass 190) visa nomination. You must be committed to living in Victoria.
+ [Employment]
+ You are not required to be working to be eligible for Victorian subclass 190 visa nomination. There is no minimum work experience and hours of work requirement.
+ Living in Victoria (onshore):
 - If you are living in Victoria and work in skilled employment for an employer physically located in Victoria , you can provide an estimate of your annual earnings in your ROI . A business using a virtual office or proxy office is not considered as physically located in Victoria. Your employment does not have to be related to or the same as your nominated occupation, but your earnings must be from skilled employment in Victoria. View our Annual earnings estimation guide for information on skilled employment and what you can and cannot claim.
 - If you are not working, working in non-skilled employment, or working for an employer not physically located in Victoria, you are still eligible to apply for nomination, but you are not eligible to claim earnings in your ROI.
-  Living overseas (offshore):
+ Living overseas (offshore):
 - If you are living overseas, you are not required to claim earnings in your ROI.
-  [Commitment to Victoria]
+ [Commitment to Victoria]
 - You must be committed to living and working in Victoria.
 - State nomination cannot be transferred from one state to another.
-  [Registration of Interest]
+ [Registration of Interest]
 - To be invited to apply for Victorian visa nomination, you must submit an ROI.
 - Your ROI must be selected by us before you can apply for skilled visa nomination. An ROI is not an application for Victorian visa nomination. There is no guarantee that your ROI will be selected.
 - View our Registration of Interest page for more information on assessment and selection considerations.
-  [Age]
+ [Age]
 - You must be under 45 years of age at the time of nomination. This is a Department of Home Affairs requirement.
-  [English language]
+ [English language]
 - You must have at least Competent English external link .
 - When you submit your nomination application, we require that your English test has at least 12 weeks validity remaining. This ensures we have enough time to assess your nomination application. We cannot nominate you if your English test has expired.
-- For further information, see the Australian Government's Department of Home Affairs’ English language requirements external link page.
-  [Skills Assessment]
-- You must have a valid skills assessment in an occupation on the Australian Government’s eligible skilled occupation list external link for the visa.
+- For further information, see the Australian Government's Department of Home Affairs' English language requirements external link page.
+ [Skills Assessment]
+- You must have a valid skills assessment in an occupation on the Australian Government's eligible skilled occupation list external link for the visa.
 - Your nominated occupation in your Skills Assessment external link must match your SkillSelect Expression of Interest (EOI) with the Department of Home Affairs.
 - When you submit your nomination application, we require that your Skills Assessment external link has at least 12 weeks validity remaining. This ensures we have enough time to assess your nomination application. We cannot nominate you if your Skills Assessment has expired.
-- For Health professionals, your occupation must be consistent with your Australian Health Practitioner Regulation Agency (AHPRA) registration.
-  [SkillSelect EOI Points]
-- You must have at least 65 points on the Australian Government’s points test external link , including the 5 points for state and territory nomination.
+- For Health professionals, your occupation must be consistent with your Australian Health Practitioner Regulation Agency (AHPRA) registration.
+ [SkillSelect EOI Points]
+- You must have at least 65 points on the Australian Government's points test external link , including the 5 points for state and territory nomination.
 INVITATION TO APPLY FOR VICTORIAN NOMINATION
-  To be invited to apply for Victorian skilled visa nomination, you must firstly make or update an Expression of Interest via the Australian Government’s SkillSelect external link and then submit a Registration of Interest (ROI).
-  View our Registration of Interest page for more information on ROI assessment and selection considerations.
-  For information on how to calculate your estimated annual earnings, visit our Annual Earnings Estimation Guide page. Answers to frequently asked questions can be found on our Skilled Visa FAQs page.
+ To be invited to apply for Victorian skilled visa nomination, you must firstly make or update an Expression of Interest via the Australian Government's SkillSelect external link and then submit a Registration of Interest (ROI).
+ View our Registration of Interest page for more information on ROI assessment and selection considerations.
+ For information on how to calculate your estimated annual earnings, visit our Annual Earnings Estimation Guide page. Answers to frequently asked questions can be found on our Skilled Visa FAQs page.
 SUBMITTING A NOMINATION APPLICATION
-  [Submit your application via the portal]
-  If you are invited to apply, you or your agent (if applicable) will be notified via email.
-  You must submit your application and all documents via the Live in Melbourne portal external link . We will not accept any applications or documents via email.
-  [What documents you will need]
-  If you are invited to apply for Victorian nomination, you must submit a complete application, including all relevant evidence to support your eligibility claims.
-  In your Victorian nomination application, you may need to provide the following documents to show you meet the requirements:
+ [Submit your application via the portal]
+ If you are invited to apply, you or your agent (if applicable) will be notified via email.
+ You must submit your application and all documents via the Live in Melbourne portal external link . We will not accept any applications or documents via email.
+ [What documents you will need]
+ If you are invited to apply for Victorian nomination, you must submit a complete application, including all relevant evidence to support your eligibility claims.
+ In your Victorian nomination application, you may need to provide the following documents to show you meet the requirements:
 - passport,
 - evidence of Victorian residence.
-  During the assessment of your nomination application, we may ask for further evidence and additional documents.
-  [Living in Victoria:]
-  To prove your residence in Victoria, you may be asked to provide the following documents to show you meet the requirements:
+ During the assessment of your nomination application, we may ask for further evidence and additional documents.
+ [Living in Victoria:]
+ To prove your residence in Victoria, you may be asked to provide the following documents to show you meet the requirements:
 - bank statements for a minimum of 6 months from your main transaction account showing your salary and everyday transactions,
 - rental or lease agreements,
 - utility bills e.g. gas, water, phone, internet,
-- driver’s licence or proof of age cards.
-  If you included annual earnings in your Registration of Interest (ROI) you will also need to provide the following in your nomination application:
+- driver's licence or proof of age cards.
+ If you included annual earnings in your Registration of Interest (ROI) you will also need to provide the following in your nomination application:
 - employment contract,
 - position description detailing the duration of your employment, the hours worked per week, and duties performed,
 - payslips (at least most recent four weeks),
 - superannuation statement (showing most recent contributions), or
 - your letter of offer.
 NOMINATION APPLICATION ASSESSMENT
-  If you submit a nomination application, it will be assessed by the Victorian Government. You will be notified of the outcome by email as soon as a decision has been made.
-  [Respond within two weeks]
-  We may ask you for more information by email.
+ If you submit a nomination application, it will be assessed by the Victorian Government. You will be notified of the outcome by email as soon as a decision has been made.
+ [Respond within two weeks]
+ We may ask you for more information by email.
 - You will have two weeks to provide the requested information.
 - If you do not respond within two weeks, we may refuse your application. Please check your junk mail and ensure the email address no-reply-gems@liveinmelbourne.vic.gov.au external link is added to your list of valid email addresses.
-  [Incomplete applications]
-  You must submit a complete application, including all relevant evidence to support your eligibility claims.
-  [Do not ask for updates on your application]
-  Please do not ask for an update on your application. We assess all applications in order of when they are submitted.
-  If you have submitted a nomination application with us, you or your agent (if applicable) can check the status of your application through the Live in Melbourne portal. The average processing time for skilled visa nomination applications is 20 business days. This does not include the waiting time if we require additional information for your application.
-  The assessment team is also responsible for responding to enquiries and we prioritise assessment of applications. Unnecessary enquiries slow down application processing times.
-  [Withdrawal]
-  You can only withdraw your subclass 190 nomination application before we finalise our assessment. Please Contact Us to withdraw your nomination application.
-  For Registrations of Interest (ROIs), you must withdraw your ROI using the Live in Melbourne portal. external link
+ [Incomplete applications]
+ You must submit a complete application, including all relevant evidence to support your eligibility claims.
+ [Do not ask for updates on your application]
+ Please do not ask for an update on your application. We assess all applications in order of when they are submitted.
+ If you have submitted a nomination application with us, you or your agent (if applicable) can check the status of your application through the Live in Melbourne portal. The average processing time for skilled visa nomination applications is 20 business days. This does not include the waiting time if we require additional information for your application.
+ The assessment team is also responsible for responding to enquiries and we prioritise assessment of applications. Unnecessary enquiries slow down application processing times.
+ [Withdrawal]
+ You can only withdraw your subclass 190 nomination application before we finalise our assessment. Please Contact Us to withdraw your nomination application.
+ For Registrations of Interest (ROIs), you must withdraw your ROI using the Live in Melbourne portal. external link
 NOMINATION APPLICATION OUTCOME
-  [Once you are nominated]
-  [Nomination refusals]
-  Before submitting a Registration of Interest (ROI) make sure you meet all the minimum eligibility requirements for the visa you are seeking nomination for.
-  Your nomination application will be refused for the following reasons:
+ [Once you are nominated]
+ [Nomination refusals]
+ Before submitting a Registration of Interest (ROI) make sure you meet all the minimum eligibility requirements for the visa you are seeking nomination for.
+ Your nomination application will be refused for the following reasons:
 - You do not meet the minimum eligibility requirements.
 - You cannot provide sufficient evidence for the claims made in your ROI or SkillSelect EOI.
 - You do not respond to our requests for further information in a timely manner.
 - You provide false or misleading information.
-  Common reasons for refused applications include:
+ Common reasons for refused applications include:
 - Over-estimated earnings (for onshore).
 - Working in employment that is not eligible (for onshore).
 - Working for an employer not operating in Victoria (for onshore).
 - Living in an Australian state and territory other than Victoria (for onshore)
 - Incorrect partner points.
-- Modification of SkillSelect EOI after invitation.
+- Modification of SkillSelect EOI after invitation.
 - False and misleading information related to employment and residence.
 - Expired Skills Assessment or English language test results.
-  If you are unable to provide sufficient evidence to demonstrate the claims you make in your SkillSelect EOI and ROI, your application may be refused.
-  If your application is refused, you will not be able to submit a new application for 6 months. This ensures our resources are allocated to processing applications that meet the requirements of the visa.
-  [False and misleading information]
-  If you provide false or misleading information as part of your nomination application, your application will be refused. We may also report it to the Department of Home Affairs who can conduct their own investigation.
-  We encourage you to submit all documents unaltered, including all PDF documents in their original form and not combined into one document.
-  We conduct verification checks on many of the documents you provide to ensure that your employment matches the skill level of your nominated occupation that you outline in your SkillSelect EOI. This includes contacting employers and institutions directly to confirm whether the documents are genuine.
-  If you are aware of instances, or yourself are pressured to submit an application with false and misleading information, we encourage you to report this to the Department of Home Affairs.
-  [Review of nomination decision]
-  If your nomination application has been refused as you did not meet the eligibility requirements, you cannot request a review of your application.
-  If you believe that an error was made in assessing your nomination application, you can submit a request for us to review the application.
-  [Renomination]
-  We do not provide renomination in the following instances:
+ If you are unable to provide sufficient evidence to demonstrate the claims you make in your SkillSelect EOI and ROI, your application may be refused.
+ If your application is refused, you will not be able to submit a new application for 6 months. This ensures our resources are allocated to processing applications that meet the requirements of the visa.
+ [False and misleading information]
+ If you provide false or misleading information as part of your nomination application, your application will be refused. We may also report it to the Department of Home Affairs who can conduct their own investigation.
+ We encourage you to submit all documents unaltered, including all PDF documents in their original form and not combined into one document.
+ We conduct verification checks on many of the documents you provide to ensure that your employment matches the skill level of your nominated occupation that you outline in your SkillSelect EOI. This includes contacting employers and institutions directly to confirm whether the documents are genuine.
+ If you are aware of instances, or yourself are pressured to submit an application with false and misleading information, we encourage you to report this to the Department of Home Affairs.
+ [Review of nomination decision]
+ If your nomination application has been refused as you did not meet the eligibility requirements, you cannot request a review of your application.
+ If you believe that an error was made in assessing your nomination application, you can submit a request for us to review the application.
+ [Renomination]
+ We do not provide renomination in the following instances:
 - You do not submit your visa application within 60 days.
 - Your SkillSelect EOI was incorrect when we nominated you, including points claimed by you or your agent.
-  If an applicant has been nominated for any skilled subclass (either 190 or 491), they cannot be nominated again in the same program year.
+ If an applicant has been nominated for any skilled subclass (either 190 or 491), they cannot be nominated again in the same program year.
 YOUR NOMINATION OBLIGATIONS
-  [Declaration form]
-  If you are nominated, you must meet the nomination obligations that you signed in the declaration form .
-  [Surveys]
-  If you are nominated, we will contact you at various times.
-  In the declaration form, you agree to complete surveys if requested by, or on behalf of the Victorian Government, including a survey upon arrival and at six monthly intervals for the two years after visa grant or arrival in Australia.
-  These surveys are a condition of nomination. They provide us important feedback on our client services and policy settings. The surveys do not have an impact on your visa.
-  [Department of Home Affairs and SkillSelect]
-  The Australian Government's Department of Home Affairs external link is responsible for all visa matters. This includes once you have been nominated by the Victorian Government and have submitted your visa application.
-  Please check subclass 190 visa processing times external link published by the Department of Home Affairs.
-  All SkillSelect and Expressions of Interest (EOI) enquiries should be directed to the Department of Home Affairs.
+ [Declaration form]
+ If you are nominated, you must meet the nomination obligations that you signed in the declaration form .
+ [Surveys]
+ If you are nominated, we will contact you at various times.
+ In the declaration form, you agree to complete surveys if requested by, or on behalf of the Victorian Government, including a survey upon arrival and at six monthly intervals for the two years after visa grant or arrival in Australia.
+ These surveys are a condition of nomination. They provide us important feedback on our client services and policy settings. The surveys do not have an impact on your visa.
+ [Department of Home Affairs and SkillSelect]
+ The Australian Government's Department of Home Affairs external link is responsible for all visa matters. This includes once you have been nominated by the Victorian Government and have submitted your visa application.
+ Please check subclass 190 visa processing times external link published by the Department of Home Affairs.
+ All SkillSelect and Expressions of Interest (EOI) enquiries should be directed to the Department of Home Affairs.
 TERMS AND CONDITIONS
-  [Can my employer or family member represent me as an agent for Victorian nomination?]
-  No, you cannot appoint an agent to act on your behalf if there are personal, financial or other interests that could, or could be seen to, influence their representation of you.
-  If a conflict of interest is identified during the application assessment, the Appointment of Agent will be deemed invalid, and the application may be refused.
-  [Nomination application fees]
-  Victorian Registration of Interest (ROI) and nomination are free of charge. When you submit your visa application with the Australian Government's Department of Home Affairs, you will need to pay the visa fee.
-  [Changes to eligibility requirements]
-  All visa nomination eligibility requirements and priorities are subject to change throughout the year without notice.
-  Any changes made are effective immediately, regardless of when your SkillSelect Expression of Interest (EOI) was submitted (or amended). We strongly discourage changing your circumstances to meet the visa nomination criteria.
-  The Victorian Government endeavours to ensure all information on the Live in Melbourne website reflects the current eligibility requirements. The Live in Melbourne website is the authoritative source for information about Victoria's skilled visa nomination program.</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+ [Can my employer or family member represent me as an agent for Victorian nomination?]
+ No, you cannot appoint an agent to act on your behalf if there are personal, financial or other interests that could, or could be seen to, influence their representation of you.
+ If a conflict of interest is identified during the application assessment, the Appointment of Agent will be deemed invalid, and the application may be refused.
+ [Nomination application fees]
+ Victorian Registration of Interest (ROI) and nomination are free of charge. When you submit your visa application with the Australian Government's Department of Home Affairs, you will need to pay the visa fee.
+ [Changes to eligibility requirements]
+ All visa nomination eligibility requirements and priorities are subject to change throughout the year without notice.
+ Any changes made are effective immediately, regardless of when your SkillSelect Expression of Interest (EOI) was submitted (or amended). We strongly discourage changing your circumstances to meet the visa nomination criteria.
+ The Victorian Government endeavours to ensure all information on the Live in Melbourne website reflects the current eligibility requirements. The Live in Melbourne website is the authoritative source for information about Victoria's skilled visa nomination program.</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+    <row r="3" ht="409" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Skilled_Work_Regional_Visa_Subclass_491</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>Subclass_491</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>BASIC ELIGIBILITY
-  To be considered for Victorian skilled visa nomination, you must:
+ To be considered for Victorian skilled visa nomination, you must:
 - Meet all the Department of Home Affairs - subclass 491 Skilled Work Regional (Provisional) visa requirements external link .
-- Meet all the Victorian Government’s - subclass 491Skilled Nominated visa requirements.
+- Meet all the Victorian Government's - subclass 491Skilled Nominated visa requirements.
 VICTORIAN SUBCLASS 491 SKILLED WORK REGIONAL VISA NOMINATION
-  [Who can apply?]
-  To be eligible to apply for Skilled Work Regional (Provisional) visa (subclass 491) nomination, you must:
+ [Who can apply?]
+ To be eligible to apply for Skilled Work Regional (Provisional) visa (subclass 491) nomination, you must:
 - be one of the following: living offshore living and working in regional Victoria.
 - be committed to living and working in regional Victoria,
 - have had your Registration of Interest (ROI) selected,
 - be under 45 years of age,
 - have at least Competent English external link ,
 - have a valid skills assessment external link in an occupation on the eligible skilled occupation list external link for this visa,
-- have achieved at least 65 points external link on the Australian Government’s points test for your Expression of Interest (EOI) in SkillSelect external link .
+- have achieved at least 65 points external link on the Australian Government's points test for your Expression of Interest (EOI) in SkillSelect external link .
 - living offshore
 - living and working in regional Victoria.
-  [How to apply?]
-  To apply for Victorian visa nomination, you must:
+ [How to apply?]
+ To apply for Victorian visa nomination, you must:
 FURTHER ELIGIBILITY REQUIREMENTS
-  [Living overseas]
-  Residence
-  If you are living overseas (offshore), you are eligible to apply for Skilled Work Regional (Provisional) visa (subclass 491) visa nomination.
-  Once you are granted the subclass 491 visa you will be required to relocate to regional Victoria. The conditions of the subclass 491 visa require you, and any dependent applicants, to live, work, and study in a designated regional area.
-  Employment
-  If you are living overseas, you are not required to claim earnings in your ROI .
-  [Living in Victoria]
-  Residence
-  You must be living in regional Victoria external link .
-- Some outer suburbs of Melbourne are considered regional for the purposes of migration by the Australian's Government's Department of Home Affairs. For example, the Mornington Peninsula, Pakenham and Geelong are considered designated regional areas of Victoria for migration purposes.
+ [Living overseas]
+ Residence
+ If you are living overseas (offshore), you are eligible to apply for Skilled Work Regional (Provisional) visa (subclass 491) visa nomination.
+ Once you are granted the subclass 491 visa you will be required to relocate to regional Victoria. The conditions of the subclass 491 visa require you, and any dependent applicants, to live, work, and study in a designated regional area.
+ Employment
+ If you are living overseas, you are not required to claim earnings in your ROI .
+ [Living in Victoria]
+ Residence
+ You must be living in regional Victoria external link .
+- Some outer suburbs of Melbourne are considered regional for the purposes of migration by the Australian's Government's Department of Home Affairs. For example, the Mornington Peninsula, Pakenham and Geelong are considered designated regional areas of Victoria for migration purposes.
 - You can find information about the designated regional areas external link on the Department of Home Affairs website.
 - We make case-by-case exceptions for those living in border communities.
-  The conditions of the subclass 491 visa require you, and any dependent applicants, to live, work, and study in a designated regional area.
-  Employment
-- You must be working in skilled employment for an employer physically located in regional Victoria. A business using a virtual office or proxy office is not considered as physically located in regional Victoria.
+ The conditions of the subclass 491 visa require you, and any dependent applicants, to live, work, and study in a designated regional area.
+ Employment
+- You must be working in skilled employment for an employer physically located in regional Victoria. A business using a virtual office or proxy office is not considered as physically located in regional Victoria.
 - A business using a virtual office or proxy office is not considered as physically located in regional Victoria.
-- You must provide an estimate of your annual earnings in your ROI . Your earnings must be from skilled employment in regional Victoria. View our Annual earnings estimation guide for information on skilled employment and what you can and cannot claim.
+- You must provide an estimate of your annual earnings in your ROI . Your earnings must be from skilled employment in regional Victoria. View our Annual earnings estimation guide for information on skilled employment and what you can and cannot claim.
 - View our Annual earnings estimation guide for information on skilled employment and what you can and cannot claim.
 - Your employment does not have to be related to or the same as your nominated occupation.
 - There is no minimum requirement for hours worked.
 - If you are not working, working in non-skilled employment, or working for an employer who is not physically located in regional Victoria, you are not eligible to apply for nomination.
-  [Commitment to regional Victoria]
+ [Commitment to regional Victoria]
 - You must be committed to living and working in a designated regional area of Victoria external link .
 - State nomination cannot be transferred from one state to another.
-  [Registration of Interest]
+ [Registration of Interest]
 - To be invited to apply for Victorian visa nomination, you must submit an ROI.
 - Your ROI must be selected by us before you can apply for skilled visa nomination. An ROI is not an application for Victorian visa nomination. There is no guarantee that your ROI will be selected.
 - View our Registration of Interest page for more information on assessment and selection considerations.
-  [Age]
+ [Age]
 - You must be under 45 years of age at the time of nomination. This is a Department of Home Affairs requirement.
-  [English language]
+ [English language]
 - You must have at least Competent English external link .
 - When you submit your nomination application, we require that your English language test has at least 12 weeks validity remaining. This ensures we have enough time to assess your nomination application. We cannot nominate you if your English language test has expired.
 - For further information, see the Australian Government's Department of Home Affairs English language requirements external link page.
-  [Skills Assessment]
+ [Skills Assessment]
 - You must have a valid skills assessment in an occupation on the eligible skilled occupation list external link for the visa.
 - Your nominated occupation in your Skills Assessment external link must match your Expression of Interest with the Department of Home Affairs.
 - When you submit your nomination application, we require that your Skills Assessment has at least 12 weeks validity remaining. This ensures we have enough time to assess your nomination application. We cannot nominate you if your Skills Assessment has expired.
-- For Health professionals, your occupation must be consistent with your Australian Health Practitioner Regulation Agency (AHPRA) registration.
-  [SkillSelect EOI Points]
-- You must have at least 65 points external link on the Australian Government’s points test external link , including the 15 points for state and territory nomination.
+- For Health professionals, your occupation must be consistent with your Australian Health Practitioner Regulation Agency (AHPRA) registration.
+ [SkillSelect EOI Points]
+- You must have at least 65 points external link on the Australian Government's points test external link , including the 15 points for state and territory nomination.
 INVITATION TO APPLY FOR VICTORIAN NOMINATION
-  To be invited to apply for Victorian skilled visa nomination, you must firstly submit or update an Expression of Interest via the Australian Government’s SkillSelect and then submit a Registration of Interest (ROI).
-  View our Registration of Interest page for more information on ROI assessment and selection considerations.
-  For information on how to calculate your estimated annual earnings, visit our Annual Earnings Estimation Guide page. Answers to frequently asked questions can be found on our Skilled Visa FAQs page.
+ To be invited to apply for Victorian skilled visa nomination, you must firstly submit or update an Expression of Interest via the Australian Government's SkillSelect and then submit a Registration of Interest (ROI).
+ View our Registration of Interest page for more information on ROI assessment and selection considerations.
+ For information on how to calculate your estimated annual earnings, visit our Annual Earnings Estimation Guide page. Answers to frequently asked questions can be found on our Skilled Visa FAQs page.
 SUBMITTING A NOMINATION APPLICATION
-  [Submit your application via the portal]
-  If you are invited to apply, you or your agent (if applicable) will be notified via email.
-  You must submit your application and all documents via the Live in Melbourne portal external link . We will not accept any applications or documents via email.
-  [What documents you will need]
-  If you are invited to apply for Victorian nomination, you must submit a complete application, including all relevant evidence to support your eligibility claims.
-  In your Victorian nomination application, you may need to provide the following documents to show you meet the requirements:
+ [Submit your application via the portal]
+ If you are invited to apply, you or your agent (if applicable) will be notified via email.
+ You must submit your application and all documents via the Live in Melbourne portal external link . We will not accept any applications or documents via email.
+ [What documents you will need]
+ If you are invited to apply for Victorian nomination, you must submit a complete application, including all relevant evidence to support your eligibility claims.
+ In your Victorian nomination application, you may need to provide the following documents to show you meet the requirements:
 - passport,
 - evidence of Victorian residence.
-  During the assessment of your nomination application, we may ask for further evidence and additional documents.
-  Living in regional Victoria:
-  To prove your residence in regional Victoria, you may be asked to provide the following documents to show you meet the requirements:
+ During the assessment of your nomination application, we may ask for further evidence and additional documents.
+ Living in regional Victoria:
+ To prove your residence in regional Victoria, you may be asked to provide the following documents to show you meet the requirements:
 - bank statements for a minimum of 6 months from your main transaction account showing your salary and everyday transactions,
 - rental or lease agreements,
 - utility bills e.g. gas, water, phone, internet,
-- driver’s licence or proof of age cards.
-  If you included annual earnings in your Registration of Interest (ROI) you will also need to provide the following in your nomination application:
+- driver's licence or proof of age cards.
+ If you included annual earnings in your Registration of Interest (ROI) you will also need to provide the following in your nomination application:
 - employment contract,
 - position description detailing the duration of your employment, the hours worked per week and duties performed
 - payslips (at least most recent four weeks),
 - superannuation statement (showing most recent contributions),
 - your letter of offer.
 NOMINATION APPLICATION ASSESSMENT
-  Following submission of your nomination application, you will be notified of the outcome by email as soon as a decision has been made.
-  [Respond within two weeks]
-  We may ask you for more information by email.
+ Following submission of your nomination application, you will be notified of the outcome by email as soon as a decision has been made.
+ [Respond within two weeks]
+ We may ask you for more information by email.
 - You will have two weeks to provide the requested information.
 - If you do not respond within two weeks, we may refuse your application. Please check your junk mail and ensure the email address no-reply-gems@liveinmelbourne.vic.gov.au external link is added to your list of valid email addresses.‎‎‎
-  [Incomplete applications]
-  You must submit a complete application, including all relevant evidence to support your eligibility claims.
-  [Please do not ask for updates on your application]
-  Please do not ask for an update on your application. We assess all applications in order of when they are submitted.
-  If you have submitted a nomination application, you or your agent (if applicable) can check the status of your application through the Live in Melbourne portal. external link The average processing time for skilled visa nomination applications is 20 business days. This does not include the waiting time if we require additional information for your application.
-  The assessment team is also responsible for responding to enquiries and we prioritise assessment of applications. Unnecessary enquiries slow down application processing times.
-  [Withdrawal]
-  You can only withdraw your subclass 491 nomination application before we finalise our assessment. Please Contact Us to withdraw your nomination application.
-  For Registrations of Interest (ROI), you must withdraw your ROI using the Live in Melbourne portal external link .
+ [Incomplete applications]
+ You must submit a complete application, including all relevant evidence to support your eligibility claims.
+ [Please do not ask for updates on your application]
+ Please do not ask for an update on your application. We assess all applications in order of when they are submitted.
+ If you have submitted a nomination application, you or your agent (if applicable) can check the status of your application through the Live in Melbourne portal. external link The average processing time for skilled visa nomination applications is 20 business days. This does not include the waiting time if we require additional information for your application.
+ The assessment team is also responsible for responding to enquiries and we prioritise assessment of applications. Unnecessary enquiries slow down application processing times.
+ [Withdrawal]
+ You can only withdraw your subclass 491 nomination application before we finalise our assessment. Please Contact Us to withdraw your nomination application.
+ For Registrations of Interest (ROI), you must withdraw your ROI using the Live in Melbourne portal external link .
 NOMINATION APPLICATION OUTCOME
-  [Once you are nominated]
-  [Nomination refusals]
-  Before submitting a Registration of Interest (ROI) make sure you meet all the minimum eligibility requirements for the visa you are seeking nomination for.
-  Your nomination application will be refused for the following reasons:
+ [Once you are nominated]
+ [Nomination refusals]
+ Before submitting a Registration of Interest (ROI) make sure you meet all the minimum eligibility requirements for the visa you are seeking nomination for.
+ Your nomination application will be refused for the following reasons:
 - You do not meet the minimum eligibility requirements.
 - You cannot provide sufficient evidence for the claims made in your ROI or SkillSelect EOI.
 - You provide false or misleading information.
 - You do not respond to our requests for further information in a timely manner.
-  Common reasons for refused applications include:
+ Common reasons for refused applications include:
 - Over-estimated earnings (for onshore).
 - Working in a non-skilled employment (for onshore).
 - Working for an employer not operating in regional Victoria (for onshore).
@@ -734,45 +743,45 @@
 - Modification of your SkillSelect EOI after invitation.
 - Integrity concerns with residence and employment claims.
 - Skills assessment or English language test result expired.
-  If you are unable to provide sufficient evidence to demonstrate the claims you make in your SkillSelect EOI and ROI, your application may be refused.
-  If your application is refused, you will not be able to submit a new application for 6 months. This ensures our resources are allocated to processing applications that meet the requirements of the visa.
-  [False and misleading information]
-  If you provide false or misleading information as part of your nomination application, your application will be refused. We may also report it to the Department of Home Affairs who can conduct their own investigation.
-  We encourage you to submit all documents unaltered, including all PDF documents in their original form and not combined into one document.
-  We conduct verification checks on many of the documents you provide to ensure that your employment matches the skill level of your nominated occupation that you outline in your SkillSelect EOI. This includes contacting employers and institutions directly to confirm whether the documents are genuine.
-  If you are aware of instances, or yourself are pressured to submit an application with false and misleading information, we encourage you to report this to the Department of Home Affairs.
-  [Review of nomination decision]
-  If your nomination application has been refused as you did not meet the eligibility requirements, you cannot request a review of your application.
-  If you believe that an error was made in assessing your nomination application, you can submit a request for us to review the application.
-  [Renomination]
-  We do not provide renomination in the following instances:
+ If you are unable to provide sufficient evidence to demonstrate the claims you make in your SkillSelect EOI and ROI, your application may be refused.
+ If your application is refused, you will not be able to submit a new application for 6 months. This ensures our resources are allocated to processing applications that meet the requirements of the visa.
+ [False and misleading information]
+ If you provide false or misleading information as part of your nomination application, your application will be refused. We may also report it to the Department of Home Affairs who can conduct their own investigation.
+ We encourage you to submit all documents unaltered, including all PDF documents in their original form and not combined into one document.
+ We conduct verification checks on many of the documents you provide to ensure that your employment matches the skill level of your nominated occupation that you outline in your SkillSelect EOI. This includes contacting employers and institutions directly to confirm whether the documents are genuine.
+ If you are aware of instances, or yourself are pressured to submit an application with false and misleading information, we encourage you to report this to the Department of Home Affairs.
+ [Review of nomination decision]
+ If your nomination application has been refused as you did not meet the eligibility requirements, you cannot request a review of your application.
+ If you believe that an error was made in assessing your nomination application, you can submit a request for us to review the application.
+ [Renomination]
+ We do not provide renomination in the following instances:
 - You do not submit your visa application within 60 days.
 - Your SkillSelect EOI was incorrect when we nominated you, including points claimed by you or your agent.
-  If an applicant has been nominated for any skilled visa (either subclass 190 or 491), they cannot be nominated again in the same program year.
+ If an applicant has been nominated for any skilled visa (either subclass 190 or 491), they cannot be nominated again in the same program year.
 YOUR NOMINATION OBLIGATIONS
-  [Declaration form]
-  If you are nominated, you must meet the nomination obligations that you signed in the declaration form .
-  [Surveys]
-  If you are nominated, we will contact you at various times.
-  In the declaration form, you agree to complete surveys if requested by, or on behalf of the Victorian Government, including a survey upon arrival and at six monthly intervals for the three years after visa grant or arrival in Australia.
-  These surveys are a condition of nomination. They provide us important feedback on our client services and policy settings.
-  [Department of Home Affairs and SkillSelect]
-  The Australian Government's Department of Home Affairs external link is responsible for all visa matters. This includes once you have been nominated by the Victorian Government and have submitted your visa application.
-  Please check subclass 491 visa processing times external link published by the Department of Home Affairs.
-  All SkillSelect and Expression of Interest enquiries should be directed to the Department of Home Affairs .
+ [Declaration form]
+ If you are nominated, you must meet the nomination obligations that you signed in the declaration form .
+ [Surveys]
+ If you are nominated, we will contact you at various times.
+ In the declaration form, you agree to complete surveys if requested by, or on behalf of the Victorian Government, including a survey upon arrival and at six monthly intervals for the three years after visa grant or arrival in Australia.
+ These surveys are a condition of nomination. They provide us important feedback on our client services and policy settings.
+ [Department of Home Affairs and SkillSelect]
+ The Australian Government's Department of Home Affairs external link is responsible for all visa matters. This includes once you have been nominated by the Victorian Government and have submitted your visa application.
+ Please check subclass 491 visa processing times external link published by the Department of Home Affairs.
+ All SkillSelect and Expression of Interest enquiries should be directed to the Department of Home Affairs .
 TERMS AND CONDITIONS
-  [Can my employer or family member represent me as an agent for Victorian nomination?]
-  No, you cannot appoint an agent to act on your behalf if there are personal, financial or other interests that could, or could be seen to, influence their representation of you.
-  If a conflict of interest is identified during the application assessment, the Appointment of Agent will be deemed invalid, and the application may be refused.
-  [Nomination application fees]
-  Victorian Registration of Interest (ROI) and nomination are free of charge. When you submit your visa application with the Australian Government's Department of Home Affairs, you will need to pay the visa fee.
-  [Changes to eligibility requirements]
-  All visa nomination eligibility requirements and priorities are subject to change throughout the year without notice.
-  Any changes made are effective immediately, regardless of when your SkillSelect Expression of Interest (EOI) was submitted (or amended). We strongly discourage changing your circumstances to meet the visa nomination criteria.
-  The Victorian Government endeavours to ensure all information on the Live in Melbourne website reflects the current eligibility requirements. The Live in Melbourne website is the authoritative source for information about Victoria's skilled visa nomination program.</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+ [Can my employer or family member represent me as an agent for Victorian nomination?]
+ No, you cannot appoint an agent to act on your behalf if there are personal, financial or other interests that could, or could be seen to, influence their representation of you.
+ If a conflict of interest is identified during the application assessment, the Appointment of Agent will be deemed invalid, and the application may be refused.
+ [Nomination application fees]
+ Victorian Registration of Interest (ROI) and nomination are free of charge. When you submit your visa application with the Australian Government's Department of Home Affairs, you will need to pay the visa fee.
+ [Changes to eligibility requirements]
+ All visa nomination eligibility requirements and priorities are subject to change throughout the year without notice.
+ Any changes made are effective immediately, regardless of when your SkillSelect Expression of Interest (EOI) was submitted (or amended). We strongly discourage changing your circumstances to meet the visa nomination criteria.
+ The Victorian Government endeavours to ensure all information on the Live in Melbourne website reflects the current eligibility requirements. The Live in Melbourne website is the authoritative source for information about Victoria's skilled visa nomination program.</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/src/scrapers/output_scrape/vic/requirements_vic.xlsx
+++ b/src/scrapers/output_scrape/vic/requirements_vic.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -426,39 +441,39 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>state code</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>state stream</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>requirements</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>service fee</t>
         </is>
       </c>
     </row>
     <row r="2" ht="409" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Subclass_190</t>
         </is>
       </c>
-      <c r="C2" s="1" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>BASIC ELIGIBILITY
  To be considered for Victorian skilled visa nomination, you must:
@@ -605,24 +620,24 @@
  The Victorian Government endeavours to ensure all information on the Live in Melbourne website reflects the current eligibility requirements. The Live in Melbourne website is the authoritative source for information about Victoria's skilled visa nomination program.</t>
         </is>
       </c>
-      <c r="D2" s="1" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="3" ht="409" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>VIC</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Subclass_491</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>BASIC ELIGIBILITY
  To be considered for Victorian skilled visa nomination, you must:
@@ -781,7 +796,7 @@
  The Victorian Government endeavours to ensure all information on the Live in Melbourne website reflects the current eligibility requirements. The Live in Melbourne website is the authoritative source for information about Victoria's skilled visa nomination program.</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
